--- a/TT SQL.xlsx
+++ b/TT SQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a627a2307563fd2c/ドキュメント/たちばな祭2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{0DDC084E-11D7-4095-9B76-E25563BD37F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E9CA23-D5E8-4B65-B8BA-269BA59CE3E8}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{0DDC084E-11D7-4095-9B76-E25563BD37F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89F35A57-A478-4B2D-9314-F203900A549F}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="タイムテーブル" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>part1 ① start</t>
   </si>
@@ -125,19 +125,7 @@
     <t>アコギ</t>
   </si>
   <si>
-    <t>fc9d2521-a6ff-49de-acd2-e6b52b6fad18</t>
-  </si>
-  <si>
-    <t>decb8b8d-f8a3-4f3a-a339-1a1c36bf1cf9</t>
-  </si>
-  <si>
-    <t>294e2eb1-6606-491d-be0f-e0e33503f445</t>
-  </si>
-  <si>
-    <t>ce06bfd2-ef92-4124-9c70-a1d540e8954b</t>
-  </si>
-  <si>
-    <t>de05824f-00f5-4557-a84c-e1b76606e34e</t>
+    <t>761c6d9d-542f-4c08-8bb0-9788029a5a71</t>
   </si>
 </sst>
 </file>
@@ -197,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -273,36 +261,6 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FFF8F9FA"/>
       </left>
       <right style="medium">
@@ -348,52 +306,7 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
         <color rgb="FFF8F9FA"/>
@@ -410,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -428,62 +341,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="21" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1313,7 +1190,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Form_Responses3_2" displayName="Form_Responses3_2" ref="A1:Y6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Form_Responses3_2" displayName="Form_Responses3_2" ref="A1:Y2">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="group_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="part1 ① start"/>
@@ -1546,7 +1423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y95"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.77734375" bestFit="1" customWidth="1"/>
@@ -1631,203 +1508,89 @@
       </c>
     </row>
     <row r="2" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.47222222222222221</v>
-      </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="14">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="K2" s="14">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="L2" s="14">
-        <v>0.625</v>
-      </c>
-      <c r="M2" s="14">
-        <v>0.63888888888888884</v>
-      </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="14">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="S2" s="14">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="T2" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="U2" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="V2" s="14">
-        <v>0.47222222222222221</v>
-      </c>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="17"/>
-    </row>
-    <row r="3" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C3" s="19">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="19">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="S3" s="19">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="21"/>
-    </row>
-    <row r="4" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="K4" s="24">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="25"/>
-    </row>
-    <row r="5" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="18">
-        <v>0.46875</v>
-      </c>
-      <c r="C5" s="19">
-        <v>0.49652777777777779</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="19">
-        <v>0.46875</v>
-      </c>
-      <c r="S5" s="19">
-        <v>0.49652777777777779</v>
-      </c>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="21"/>
-    </row>
-    <row r="6" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="S6" s="10">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="12"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="13"/>
+    </row>
+    <row r="3" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="R3" s="6"/>
+      <c r="T3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="5"/>
+      <c r="Y3" s="8"/>
+    </row>
+    <row r="4" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="R4" s="6"/>
+      <c r="T4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="5"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="R5" s="6"/>
+      <c r="T5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="5"/>
+      <c r="Y5" s="8"/>
+    </row>
+    <row r="6" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="R6" s="6"/>
+      <c r="T6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="5"/>
+      <c r="Y6" s="8"/>
     </row>
     <row r="7" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C7" s="5"/>
@@ -1899,7 +1662,7 @@
       <c r="W11" s="5"/>
       <c r="Y11" s="8"/>
     </row>
-    <row r="12" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="5"/>
       <c r="E12" s="5"/>
       <c r="G12" s="5"/>
@@ -1913,13 +1676,15 @@
       <c r="W12" s="5"/>
       <c r="Y12" s="8"/>
     </row>
-    <row r="13" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="5"/>
       <c r="E13" s="5"/>
       <c r="G13" s="5"/>
       <c r="J13" s="6"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="O13" s="5"/>
       <c r="R13" s="6"/>
       <c r="T13" s="7"/>
@@ -1927,13 +1692,15 @@
       <c r="W13" s="5"/>
       <c r="Y13" s="8"/>
     </row>
-    <row r="14" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="5"/>
       <c r="E14" s="5"/>
       <c r="G14" s="5"/>
       <c r="J14" s="6"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="O14" s="5"/>
       <c r="R14" s="6"/>
       <c r="T14" s="7"/>
@@ -1941,13 +1708,15 @@
       <c r="W14" s="5"/>
       <c r="Y14" s="8"/>
     </row>
-    <row r="15" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="5"/>
       <c r="E15" s="5"/>
       <c r="G15" s="5"/>
       <c r="J15" s="6"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="O15" s="5"/>
       <c r="R15" s="6"/>
       <c r="T15" s="7"/>
@@ -1961,7 +1730,9 @@
       <c r="G16" s="5"/>
       <c r="J16" s="6"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="O16" s="5"/>
       <c r="R16" s="6"/>
       <c r="T16" s="7"/>
@@ -1975,8 +1746,8 @@
       <c r="G17" s="5"/>
       <c r="J17" s="6"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="26" t="s">
-        <v>25</v>
+      <c r="M17" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="O17" s="5"/>
       <c r="R17" s="6"/>
@@ -1985,15 +1756,13 @@
       <c r="W17" s="5"/>
       <c r="Y17" s="8"/>
     </row>
-    <row r="18" spans="3:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C18" s="5"/>
       <c r="E18" s="5"/>
       <c r="G18" s="5"/>
       <c r="J18" s="6"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="27" t="s">
-        <v>26</v>
-      </c>
+      <c r="M18" s="5"/>
       <c r="O18" s="5"/>
       <c r="R18" s="6"/>
       <c r="T18" s="7"/>
@@ -2001,15 +1770,13 @@
       <c r="W18" s="5"/>
       <c r="Y18" s="8"/>
     </row>
-    <row r="19" spans="3:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C19" s="5"/>
       <c r="E19" s="5"/>
       <c r="G19" s="5"/>
       <c r="J19" s="6"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="28" t="s">
-        <v>27</v>
-      </c>
+      <c r="M19" s="5"/>
       <c r="O19" s="5"/>
       <c r="R19" s="6"/>
       <c r="T19" s="7"/>
@@ -2017,15 +1784,13 @@
       <c r="W19" s="5"/>
       <c r="Y19" s="8"/>
     </row>
-    <row r="20" spans="3:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C20" s="5"/>
       <c r="E20" s="5"/>
       <c r="G20" s="5"/>
       <c r="J20" s="6"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="27" t="s">
-        <v>28</v>
-      </c>
+      <c r="M20" s="5"/>
       <c r="O20" s="5"/>
       <c r="R20" s="6"/>
       <c r="T20" s="7"/>
@@ -2033,15 +1798,13 @@
       <c r="W20" s="5"/>
       <c r="Y20" s="8"/>
     </row>
-    <row r="21" spans="3:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C21" s="5"/>
       <c r="E21" s="5"/>
       <c r="G21" s="5"/>
       <c r="J21" s="6"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="29" t="s">
-        <v>29</v>
-      </c>
+      <c r="M21" s="5"/>
       <c r="O21" s="5"/>
       <c r="R21" s="6"/>
       <c r="T21" s="7"/>
@@ -3085,62 +2848,6 @@
       <c r="W95" s="5"/>
       <c r="Y95" s="8"/>
     </row>
-    <row r="96" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="J96" s="6"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="5"/>
-      <c r="O96" s="5"/>
-      <c r="R96" s="6"/>
-      <c r="T96" s="7"/>
-      <c r="V96" s="7"/>
-      <c r="W96" s="5"/>
-      <c r="Y96" s="8"/>
-    </row>
-    <row r="97" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="J97" s="6"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="5"/>
-      <c r="O97" s="5"/>
-      <c r="R97" s="6"/>
-      <c r="T97" s="7"/>
-      <c r="V97" s="7"/>
-      <c r="W97" s="5"/>
-      <c r="Y97" s="8"/>
-    </row>
-    <row r="98" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="J98" s="6"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="R98" s="6"/>
-      <c r="T98" s="7"/>
-      <c r="V98" s="7"/>
-      <c r="W98" s="5"/>
-      <c r="Y98" s="8"/>
-    </row>
-    <row r="99" spans="3:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="J99" s="6"/>
-      <c r="L99" s="7"/>
-      <c r="M99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="R99" s="6"/>
-      <c r="T99" s="7"/>
-      <c r="V99" s="7"/>
-      <c r="W99" s="5"/>
-      <c r="Y99" s="8"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
